--- a/web-reports/latest/Excel/Passed_Test_Cases.xlsx
+++ b/web-reports/latest/Excel/Passed_Test_Cases.xlsx
@@ -2960,7 +2960,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -2994,7 +2994,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
@@ -3028,7 +3028,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>8</v>
@@ -3062,7 +3062,7 @@
         <v>26</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>8</v>
@@ -3079,7 +3079,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
@@ -3096,7 +3096,7 @@
         <v>30</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>8</v>
@@ -3113,7 +3113,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -3130,7 +3130,7 @@
         <v>34</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>8</v>
@@ -3147,7 +3147,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>38</v>
       </c>
       <c r="D17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>8</v>
@@ -3198,7 +3198,7 @@
         <v>42</v>
       </c>
       <c r="D19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>8</v>
@@ -3215,7 +3215,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>8</v>
@@ -3266,7 +3266,7 @@
         <v>50</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>8</v>
@@ -3283,7 +3283,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>8</v>
@@ -3317,7 +3317,7 @@
         <v>56</v>
       </c>
       <c r="D26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>8</v>
@@ -3351,7 +3351,7 @@
         <v>60</v>
       </c>
       <c r="D28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
@@ -3368,7 +3368,7 @@
         <v>62</v>
       </c>
       <c r="D29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>64</v>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>8</v>
@@ -3419,7 +3419,7 @@
         <v>68</v>
       </c>
       <c r="D32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>8</v>
@@ -3453,7 +3453,7 @@
         <v>72</v>
       </c>
       <c r="D34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>8</v>
@@ -3487,7 +3487,7 @@
         <v>76</v>
       </c>
       <c r="D36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>8</v>
@@ -3521,7 +3521,7 @@
         <v>80</v>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>8</v>
@@ -3538,7 +3538,7 @@
         <v>82</v>
       </c>
       <c r="D39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>86</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>8</v>
@@ -3589,7 +3589,7 @@
         <v>89</v>
       </c>
       <c r="D42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>8</v>
@@ -3708,7 +3708,7 @@
         <v>103</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>8</v>
@@ -3742,7 +3742,7 @@
         <v>107</v>
       </c>
       <c r="D51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>8</v>
@@ -3776,7 +3776,7 @@
         <v>111</v>
       </c>
       <c r="D53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>8</v>
@@ -3810,7 +3810,7 @@
         <v>115</v>
       </c>
       <c r="D55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>117</v>
       </c>
       <c r="D56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>8</v>
@@ -3912,7 +3912,7 @@
         <v>127</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>8</v>
@@ -4014,7 +4014,7 @@
         <v>139</v>
       </c>
       <c r="D67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>8</v>
@@ -4048,7 +4048,7 @@
         <v>143</v>
       </c>
       <c r="D69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>8</v>
@@ -4337,7 +4337,7 @@
         <v>177</v>
       </c>
       <c r="D86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>8</v>
@@ -4405,7 +4405,7 @@
         <v>185</v>
       </c>
       <c r="D90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>8</v>
@@ -4473,7 +4473,7 @@
         <v>193</v>
       </c>
       <c r="D94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>8</v>
@@ -4541,7 +4541,7 @@
         <v>201</v>
       </c>
       <c r="D98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>8</v>
@@ -4813,7 +4813,7 @@
         <v>234</v>
       </c>
       <c r="D114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>8</v>
@@ -5000,7 +5000,7 @@
         <v>256</v>
       </c>
       <c r="D125" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>8</v>
@@ -5085,7 +5085,7 @@
         <v>266</v>
       </c>
       <c r="D130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>8</v>
@@ -5170,7 +5170,7 @@
         <v>276</v>
       </c>
       <c r="D135" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>8</v>
@@ -5272,7 +5272,7 @@
         <v>288</v>
       </c>
       <c r="D141" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>8</v>
@@ -5340,7 +5340,7 @@
         <v>296</v>
       </c>
       <c r="D145" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>8</v>
@@ -5408,7 +5408,7 @@
         <v>304</v>
       </c>
       <c r="D149" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>8</v>
@@ -5527,7 +5527,7 @@
         <v>319</v>
       </c>
       <c r="D156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>8</v>
@@ -5561,7 +5561,7 @@
         <v>323</v>
       </c>
       <c r="D158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>8</v>
@@ -5629,7 +5629,7 @@
         <v>331</v>
       </c>
       <c r="D162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>8</v>
@@ -5646,7 +5646,7 @@
         <v>333</v>
       </c>
       <c r="D163" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>8</v>
@@ -5816,7 +5816,7 @@
         <v>353</v>
       </c>
       <c r="D173" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>8</v>
@@ -5969,7 +5969,7 @@
         <v>371</v>
       </c>
       <c r="D182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>8</v>
@@ -6020,7 +6020,7 @@
         <v>377</v>
       </c>
       <c r="D185" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>379</v>
       </c>
       <c r="D186" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>8</v>
@@ -6105,7 +6105,7 @@
         <v>387</v>
       </c>
       <c r="D190" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>8</v>
@@ -6139,7 +6139,7 @@
         <v>391</v>
       </c>
       <c r="D192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>8</v>
@@ -6377,7 +6377,7 @@
         <v>420</v>
       </c>
       <c r="D206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>8</v>
@@ -6394,7 +6394,7 @@
         <v>422</v>
       </c>
       <c r="D207" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>8</v>
@@ -6428,7 +6428,7 @@
         <v>426</v>
       </c>
       <c r="D209" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>8</v>
@@ -6683,7 +6683,7 @@
         <v>456</v>
       </c>
       <c r="D224" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>8</v>
@@ -6734,7 +6734,7 @@
         <v>462</v>
       </c>
       <c r="D227" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>8</v>
@@ -7023,7 +7023,7 @@
         <v>496</v>
       </c>
       <c r="D244" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>8</v>
@@ -7040,7 +7040,7 @@
         <v>498</v>
       </c>
       <c r="D245" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>8</v>
@@ -7159,7 +7159,7 @@
         <v>512</v>
       </c>
       <c r="D252" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>8</v>
@@ -7482,7 +7482,7 @@
         <v>551</v>
       </c>
       <c r="D271" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>8</v>
@@ -8094,7 +8094,7 @@
         <v>623</v>
       </c>
       <c r="D307" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>8</v>
@@ -8774,7 +8774,7 @@
         <v>703</v>
       </c>
       <c r="D347" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>8</v>
@@ -9063,7 +9063,7 @@
         <v>737</v>
       </c>
       <c r="D364" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>8</v>
@@ -9097,7 +9097,7 @@
         <v>741</v>
       </c>
       <c r="D366" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>8</v>
@@ -9675,7 +9675,7 @@
         <v>809</v>
       </c>
       <c r="D400" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>8</v>

--- a/web-reports/latest/Excel/Passed_Test_Cases.xlsx
+++ b/web-reports/latest/Excel/Passed_Test_Cases.xlsx
@@ -2960,7 +2960,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -2994,7 +2994,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>8</v>
@@ -3079,7 +3079,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
@@ -3113,7 +3113,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -3198,7 +3198,7 @@
         <v>42</v>
       </c>
       <c r="D19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>8</v>
@@ -3232,7 +3232,7 @@
         <v>46</v>
       </c>
       <c r="D21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>8</v>
@@ -3266,7 +3266,7 @@
         <v>50</v>
       </c>
       <c r="D23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>8</v>
@@ -3283,7 +3283,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>8</v>
@@ -3487,7 +3487,7 @@
         <v>76</v>
       </c>
       <c r="D36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>8</v>
@@ -3504,7 +3504,7 @@
         <v>78</v>
       </c>
       <c r="D37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>8</v>
@@ -3521,7 +3521,7 @@
         <v>80</v>
       </c>
       <c r="D38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>8</v>
@@ -3555,7 +3555,7 @@
         <v>84</v>
       </c>
       <c r="D40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>86</v>
       </c>
       <c r="D41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>8</v>
@@ -3589,7 +3589,7 @@
         <v>89</v>
       </c>
       <c r="D42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>8</v>
@@ -3708,7 +3708,7 @@
         <v>103</v>
       </c>
       <c r="D49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>8</v>
@@ -3742,7 +3742,7 @@
         <v>107</v>
       </c>
       <c r="D51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>8</v>
@@ -3810,7 +3810,7 @@
         <v>115</v>
       </c>
       <c r="D55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>117</v>
       </c>
       <c r="D56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>8</v>
@@ -3844,7 +3844,7 @@
         <v>119</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
@@ -4014,7 +4014,7 @@
         <v>139</v>
       </c>
       <c r="D67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>8</v>
@@ -4048,7 +4048,7 @@
         <v>143</v>
       </c>
       <c r="D69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>8</v>
@@ -4082,7 +4082,7 @@
         <v>147</v>
       </c>
       <c r="D71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>8</v>
@@ -4116,7 +4116,7 @@
         <v>151</v>
       </c>
       <c r="D73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>8</v>
@@ -4235,7 +4235,7 @@
         <v>165</v>
       </c>
       <c r="D80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>8</v>
@@ -4337,7 +4337,7 @@
         <v>177</v>
       </c>
       <c r="D86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>8</v>
@@ -4439,7 +4439,7 @@
         <v>189</v>
       </c>
       <c r="D92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>8</v>
@@ -4473,7 +4473,7 @@
         <v>193</v>
       </c>
       <c r="D94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>8</v>
@@ -4813,7 +4813,7 @@
         <v>234</v>
       </c>
       <c r="D114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>8</v>
@@ -5000,7 +5000,7 @@
         <v>256</v>
       </c>
       <c r="D125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>8</v>
@@ -5051,7 +5051,7 @@
         <v>262</v>
       </c>
       <c r="D128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>8</v>
@@ -5085,7 +5085,7 @@
         <v>266</v>
       </c>
       <c r="D130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>8</v>
@@ -5170,7 +5170,7 @@
         <v>276</v>
       </c>
       <c r="D135" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>8</v>
@@ -5272,7 +5272,7 @@
         <v>288</v>
       </c>
       <c r="D141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>8</v>
@@ -5340,7 +5340,7 @@
         <v>296</v>
       </c>
       <c r="D145" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>8</v>
@@ -5408,7 +5408,7 @@
         <v>304</v>
       </c>
       <c r="D149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>8</v>
@@ -5527,7 +5527,7 @@
         <v>319</v>
       </c>
       <c r="D156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>8</v>
@@ -5561,7 +5561,7 @@
         <v>323</v>
       </c>
       <c r="D158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>8</v>
@@ -5646,7 +5646,7 @@
         <v>333</v>
       </c>
       <c r="D163" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>8</v>
@@ -6020,7 +6020,7 @@
         <v>377</v>
       </c>
       <c r="D185" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>379</v>
       </c>
       <c r="D186" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>8</v>
@@ -6105,7 +6105,7 @@
         <v>387</v>
       </c>
       <c r="D190" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>8</v>
@@ -6139,7 +6139,7 @@
         <v>391</v>
       </c>
       <c r="D192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>393</v>
       </c>
       <c r="D193" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>8</v>
@@ -6394,7 +6394,7 @@
         <v>422</v>
       </c>
       <c r="D207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>8</v>
@@ -6547,7 +6547,7 @@
         <v>440</v>
       </c>
       <c r="D216" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>8</v>
@@ -6683,7 +6683,7 @@
         <v>456</v>
       </c>
       <c r="D224" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>8</v>
@@ -6717,7 +6717,7 @@
         <v>460</v>
       </c>
       <c r="D226" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>8</v>
@@ -6734,7 +6734,7 @@
         <v>462</v>
       </c>
       <c r="D227" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>8</v>
@@ -7108,7 +7108,7 @@
         <v>506</v>
       </c>
       <c r="D249" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>8</v>
@@ -7159,7 +7159,7 @@
         <v>512</v>
       </c>
       <c r="D252" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>8</v>
@@ -7414,7 +7414,7 @@
         <v>543</v>
       </c>
       <c r="D267" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>8</v>
@@ -7533,7 +7533,7 @@
         <v>557</v>
       </c>
       <c r="D274" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>8</v>
@@ -8094,7 +8094,7 @@
         <v>623</v>
       </c>
       <c r="D307" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>8</v>
@@ -8162,7 +8162,7 @@
         <v>631</v>
       </c>
       <c r="D311" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>8</v>
@@ -8434,7 +8434,7 @@
         <v>663</v>
       </c>
       <c r="D327" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>8</v>
@@ -8587,7 +8587,7 @@
         <v>681</v>
       </c>
       <c r="D336" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>8</v>
@@ -8740,7 +8740,7 @@
         <v>699</v>
       </c>
       <c r="D345" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>8</v>
@@ -8774,7 +8774,7 @@
         <v>703</v>
       </c>
       <c r="D347" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>8</v>
@@ -9063,7 +9063,7 @@
         <v>737</v>
       </c>
       <c r="D364" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>8</v>
@@ -9539,7 +9539,7 @@
         <v>793</v>
       </c>
       <c r="D392" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>8</v>
